--- a/healthcare_surveys/005_youth_climate_policy_understanding_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/005_youth_climate_policy_understanding_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -576,7 +576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0: no knowledge, 10: expert</t>
+          <t>0 - no knowledge, 10 - expert</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>policy_ideas</t>
+          <t>policy_ideas_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What do you think is missing in current climate policy?</t>
+          <t>Policy Ideas 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>policy_support</t>
+          <t>policy_support_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How you can be contacted to support climate policy?</t>
+          <t>Policy Support 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>policy_advisors</t>
+          <t>policy_advisors_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Who do you think should be the climate policy advisors?</t>
+          <t>Policy Advisors 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>policy_awareness</t>
+          <t>policy_awareness_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How do you think climate policy can be made aware of by the public?</t>
+          <t>Policy Awareness 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>policy_funding</t>
+          <t>policy_funding_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Which of the following sources can provide funding for climate policy?</t>
+          <t>Policy Funding 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>policy_implementation</t>
+          <t>policy_implementation_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>When do you think the climate policy should be implemented?</t>
+          <t>Policy Implementation 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>policy_satisfaction</t>
+          <t>policy_satisfaction_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How satisfied are you with current climate policy?</t>
+          <t>Policy Satisfaction 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
   <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1682,7 +1682,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>policy_advisors_choices</t>
+          <t>policy_advisors_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>policy_advisors_choices</t>
+          <t>policy_advisors_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1716,7 +1716,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>policy_advisors_choices</t>
+          <t>policy_advisors_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>policy_awareness_choices</t>
+          <t>policy_awareness_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1750,7 +1750,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>policy_awareness_choices</t>
+          <t>policy_awareness_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>policy_awareness_choices</t>
+          <t>policy_awareness_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>policy_funding_choices</t>
+          <t>policy_funding_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>policy_funding_choices</t>
+          <t>policy_funding_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1818,7 +1818,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>policy_funding_choices</t>
+          <t>policy_funding_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>policy_implementation_choices</t>
+          <t>policy_implementation_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>policy_implementation_choices</t>
+          <t>policy_implementation_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>policy_satisfaction_choices</t>
+          <t>policy_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>policy_satisfaction_choices</t>
+          <t>policy_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1903,7 +1903,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>policy_satisfaction_choices</t>
+          <t>policy_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
